--- a/tools/config-xlsx/drop.xlsx
+++ b/tools/config-xlsx/drop.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,6 +414,12 @@
       <c r="D1" t="str">
         <v>slotGroup</v>
       </c>
+      <c r="E1" t="str">
+        <v>levelMin</v>
+      </c>
+      <c r="F1" t="str">
+        <v>levelMax</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -428,6 +434,12 @@
       <c r="D2" t="str">
         <v>any</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -442,10 +454,16 @@
       <c r="D3" t="str">
         <v>any</v>
       </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/drop.xlsx
+++ b/tools/config-xlsx/drop.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,13 +423,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="D2" t="str">
         <v>any</v>
@@ -438,39 +438,79 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="D3" t="str">
         <v>any</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="D4" t="str">
+        <v>any</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="D5" t="str">
+        <v>any</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,7 +525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B2" t="str">
         <v>common</v>
@@ -496,7 +536,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B3" t="str">
         <v>fine</v>
@@ -507,7 +547,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B4" t="str">
         <v>rare</v>
@@ -518,7 +558,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B5" t="str">
         <v>epic</v>
@@ -529,7 +569,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>level_1</v>
+        <v>c1_early</v>
       </c>
       <c r="B6" t="str">
         <v>legend</v>
@@ -540,7 +580,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B7" t="str">
         <v>common</v>
@@ -551,7 +591,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B8" t="str">
         <v>fine</v>
@@ -562,7 +602,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B9" t="str">
         <v>rare</v>
@@ -573,7 +613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B10" t="str">
         <v>epic</v>
@@ -584,7 +624,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>level_2</v>
+        <v>c1_mid</v>
       </c>
       <c r="B11" t="str">
         <v>legend</v>
@@ -593,9 +633,119 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B12" t="str">
+        <v>common</v>
+      </c>
+      <c r="C12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B13" t="str">
+        <v>fine</v>
+      </c>
+      <c r="C13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B14" t="str">
+        <v>rare</v>
+      </c>
+      <c r="C14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B15" t="str">
+        <v>epic</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>c1_late</v>
+      </c>
+      <c r="B16" t="str">
+        <v>legend</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B17" t="str">
+        <v>common</v>
+      </c>
+      <c r="C17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B18" t="str">
+        <v>fine</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B19" t="str">
+        <v>rare</v>
+      </c>
+      <c r="C19">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B20" t="str">
+        <v>epic</v>
+      </c>
+      <c r="C20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>c1_boss</v>
+      </c>
+      <c r="B21" t="str">
+        <v>legend</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
   </ignoredErrors>
 </worksheet>
 </file>
